--- a/notebooks/Random Forest/predictions_afr_2025.xlsx
+++ b/notebooks/Random Forest/predictions_afr_2025.xlsx
@@ -476,10 +476,10 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>1.462482141955267</v>
+        <v>1.462482141955268</v>
       </c>
       <c r="D3" t="n">
-        <v>1.438262807359308</v>
+        <v>1.438262807359307</v>
       </c>
     </row>
     <row r="4">
@@ -492,7 +492,7 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>1.465613336399712</v>
+        <v>1.465613336399713</v>
       </c>
       <c r="D4" t="n">
         <v>1.43790059505772</v>
@@ -508,7 +508,7 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>1.596931855158731</v>
+        <v>1.59693185515873</v>
       </c>
       <c r="D5" t="n">
         <v>1.581449238747364</v>
@@ -572,7 +572,7 @@
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>1.062724353174602</v>
+        <v>1.062724353174603</v>
       </c>
       <c r="D9" t="n">
         <v>1.047267037698412</v>
@@ -591,7 +591,7 @@
         <v>1.382215025656695</v>
       </c>
       <c r="D10" t="n">
-        <v>1.373694588237931</v>
+        <v>1.373694588237932</v>
       </c>
     </row>
     <row r="11">
@@ -639,7 +639,7 @@
         <v>1.567724700563326</v>
       </c>
       <c r="D13" t="n">
-        <v>1.548474123362749</v>
+        <v>1.548474123362748</v>
       </c>
     </row>
     <row r="14">
@@ -652,10 +652,10 @@
         <v>2025</v>
       </c>
       <c r="C14" t="n">
-        <v>1.350658155522109</v>
+        <v>1.35065815552211</v>
       </c>
       <c r="D14" t="n">
-        <v>1.33885876657772</v>
+        <v>1.338858766577721</v>
       </c>
     </row>
     <row r="15">
@@ -716,7 +716,7 @@
         <v>2025</v>
       </c>
       <c r="C18" t="n">
-        <v>1.297026954004329</v>
+        <v>1.297026954004328</v>
       </c>
       <c r="D18" t="n">
         <v>1.266523109376734</v>
@@ -732,7 +732,7 @@
         <v>2025</v>
       </c>
       <c r="C19" t="n">
-        <v>1.640994842352092</v>
+        <v>1.640994842352093</v>
       </c>
       <c r="D19" t="n">
         <v>1.649508123737374</v>
@@ -831,7 +831,7 @@
         <v>1.387749219131208</v>
       </c>
       <c r="D25" t="n">
-        <v>1.376499329594301</v>
+        <v>1.376499329594302</v>
       </c>
     </row>
     <row r="26">
@@ -860,7 +860,7 @@
         <v>2025</v>
       </c>
       <c r="C27" t="n">
-        <v>1.244065982572983</v>
+        <v>1.244065982572982</v>
       </c>
       <c r="D27" t="n">
         <v>1.23309786550949</v>
@@ -911,7 +911,7 @@
         <v>1.395657796536796</v>
       </c>
       <c r="D30" t="n">
-        <v>1.396004954365078</v>
+        <v>1.396004954365079</v>
       </c>
     </row>
     <row r="31">
@@ -940,10 +940,10 @@
         <v>2025</v>
       </c>
       <c r="C32" t="n">
-        <v>1.436864606962482</v>
+        <v>1.436864606962483</v>
       </c>
       <c r="D32" t="n">
-        <v>1.393641678193883</v>
+        <v>1.393641678193881</v>
       </c>
     </row>
     <row r="33">
@@ -975,7 +975,7 @@
         <v>1.267765405192031</v>
       </c>
       <c r="D34" t="n">
-        <v>1.244544037948163</v>
+        <v>1.244544037948164</v>
       </c>
     </row>
     <row r="35">
@@ -988,7 +988,7 @@
         <v>2025</v>
       </c>
       <c r="C35" t="n">
-        <v>1.257693105769232</v>
+        <v>1.257693105769231</v>
       </c>
       <c r="D35" t="n">
         <v>1.236962710747586</v>
@@ -1039,7 +1039,7 @@
         <v>1.459610278860029</v>
       </c>
       <c r="D38" t="n">
-        <v>1.438452426406927</v>
+        <v>1.438452426406926</v>
       </c>
     </row>
     <row r="39">
@@ -1068,10 +1068,10 @@
         <v>2025</v>
       </c>
       <c r="C40" t="n">
-        <v>1.109357892857142</v>
+        <v>1.109357892857143</v>
       </c>
       <c r="D40" t="n">
-        <v>1.070089240079365</v>
+        <v>1.070089240079364</v>
       </c>
     </row>
     <row r="41">
@@ -1084,7 +1084,7 @@
         <v>2025</v>
       </c>
       <c r="C41" t="n">
-        <v>1.538278867560802</v>
+        <v>1.538278867560801</v>
       </c>
       <c r="D41" t="n">
         <v>1.53800001618995</v>
@@ -1103,7 +1103,7 @@
         <v>1.385726738972478</v>
       </c>
       <c r="D42" t="n">
-        <v>1.378218712711184</v>
+        <v>1.378218712711185</v>
       </c>
     </row>
     <row r="43">
@@ -1132,7 +1132,7 @@
         <v>2025</v>
       </c>
       <c r="C44" t="n">
-        <v>1.294233996392496</v>
+        <v>1.294233996392495</v>
       </c>
       <c r="D44" t="n">
         <v>1.274248689213564</v>
@@ -1164,7 +1164,7 @@
         <v>2025</v>
       </c>
       <c r="C46" t="n">
-        <v>1.381564125595359</v>
+        <v>1.381564125595358</v>
       </c>
       <c r="D46" t="n">
         <v>1.378734437278284</v>
@@ -1180,10 +1180,10 @@
         <v>2025</v>
       </c>
       <c r="C47" t="n">
-        <v>1.634954904761905</v>
+        <v>1.634954904761904</v>
       </c>
       <c r="D47" t="n">
-        <v>1.595180633241758</v>
+        <v>1.595180633241757</v>
       </c>
     </row>
     <row r="48">
@@ -1199,7 +1199,7 @@
         <v>1.738298739814925</v>
       </c>
       <c r="D48" t="n">
-        <v>1.739575057149552</v>
+        <v>1.739575057149551</v>
       </c>
     </row>
     <row r="49">
@@ -1215,7 +1215,7 @@
         <v>1.822261323023469</v>
       </c>
       <c r="D49" t="n">
-        <v>1.826936898629149</v>
+        <v>1.82693689862915</v>
       </c>
     </row>
     <row r="50">
@@ -1260,10 +1260,10 @@
         <v>2025</v>
       </c>
       <c r="C52" t="n">
-        <v>1.540493440222303</v>
+        <v>1.540493440222304</v>
       </c>
       <c r="D52" t="n">
-        <v>1.537683198873008</v>
+        <v>1.537683198873009</v>
       </c>
     </row>
     <row r="53">
@@ -1308,7 +1308,7 @@
         <v>2025</v>
       </c>
       <c r="C55" t="n">
-        <v>1.062222490079365</v>
+        <v>1.062222490079364</v>
       </c>
       <c r="D55" t="n">
         <v>1.063683490079365</v>
@@ -1324,10 +1324,10 @@
         <v>2025</v>
       </c>
       <c r="C56" t="n">
-        <v>1.656104008151796</v>
+        <v>1.656104008151795</v>
       </c>
       <c r="D56" t="n">
-        <v>1.661976572365359</v>
+        <v>1.661976572365358</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         <v>1.548067824253304</v>
       </c>
       <c r="D57" t="n">
-        <v>1.540747093650573</v>
+        <v>1.540747093650572</v>
       </c>
     </row>
     <row r="58">
@@ -1375,7 +1375,7 @@
         <v>2.459845101731603</v>
       </c>
       <c r="D59" t="n">
-        <v>2.406451995657121</v>
+        <v>2.406451995657122</v>
       </c>
     </row>
     <row r="60">
@@ -1420,10 +1420,10 @@
         <v>2025</v>
       </c>
       <c r="C62" t="n">
-        <v>1.068045865079364</v>
+        <v>1.068045865079365</v>
       </c>
       <c r="D62" t="n">
-        <v>1.053411049603174</v>
+        <v>1.053411049603175</v>
       </c>
     </row>
     <row r="63">
@@ -1455,7 +1455,7 @@
         <v>1.060571811507936</v>
       </c>
       <c r="D64" t="n">
-        <v>1.046873371031746</v>
+        <v>1.046873371031745</v>
       </c>
     </row>
     <row r="65">
@@ -1580,10 +1580,10 @@
         <v>2025</v>
       </c>
       <c r="C72" t="n">
-        <v>1.087110261904761</v>
+        <v>1.087110261904762</v>
       </c>
       <c r="D72" t="n">
-        <v>1.055320740079364</v>
+        <v>1.055320740079365</v>
       </c>
     </row>
     <row r="73">
@@ -1596,7 +1596,7 @@
         <v>2025</v>
       </c>
       <c r="C73" t="n">
-        <v>1.70771970436536</v>
+        <v>1.707719704365359</v>
       </c>
       <c r="D73" t="n">
         <v>1.702872508487407</v>
@@ -1628,7 +1628,7 @@
         <v>2025</v>
       </c>
       <c r="C75" t="n">
-        <v>1.296922121031746</v>
+        <v>1.296922121031745</v>
       </c>
       <c r="D75" t="n">
         <v>1.265085903388278</v>
@@ -1644,7 +1644,7 @@
         <v>2025</v>
       </c>
       <c r="C76" t="n">
-        <v>1.472994753066378</v>
+        <v>1.472994753066379</v>
       </c>
       <c r="D76" t="n">
         <v>1.466224592352092</v>
@@ -1676,7 +1676,7 @@
         <v>2025</v>
       </c>
       <c r="C78" t="n">
-        <v>1.441832563492063</v>
+        <v>1.441832563492064</v>
       </c>
       <c r="D78" t="n">
         <v>1.404039217939917</v>
@@ -1692,10 +1692,10 @@
         <v>2025</v>
       </c>
       <c r="C79" t="n">
-        <v>2.649130948232322</v>
+        <v>2.649130948232323</v>
       </c>
       <c r="D79" t="n">
-        <v>2.634626664502164</v>
+        <v>2.634626664502165</v>
       </c>
     </row>
     <row r="80">
@@ -1711,7 +1711,7 @@
         <v>1.384772848571354</v>
       </c>
       <c r="D80" t="n">
-        <v>1.381773772638326</v>
+        <v>1.381773772638327</v>
       </c>
     </row>
     <row r="81">
@@ -1740,10 +1740,10 @@
         <v>2025</v>
       </c>
       <c r="C82" t="n">
-        <v>1.909437232683984</v>
+        <v>1.909437232683983</v>
       </c>
       <c r="D82" t="n">
-        <v>1.906482240079364</v>
+        <v>1.906482240079365</v>
       </c>
     </row>
     <row r="83">
@@ -1807,7 +1807,7 @@
         <v>1.061944382936507</v>
       </c>
       <c r="D86" t="n">
-        <v>1.063405382936507</v>
+        <v>1.063405382936508</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/Random Forest/predictions_afr_2025.xlsx
+++ b/notebooks/Random Forest/predictions_afr_2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,12 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>СКР</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>predictions</t>
+          <t>СКР_прогноз</t>
         </is>
       </c>
     </row>
@@ -460,10 +455,7 @@
         <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>1.291373049603175</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.259137438922189</v>
+        <v>1.271219715578256</v>
       </c>
     </row>
     <row r="3">
@@ -476,10 +468,7 @@
         <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>1.462482141955268</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1.438262807359307</v>
+        <v>1.472449521797183</v>
       </c>
     </row>
     <row r="4">
@@ -492,10 +481,7 @@
         <v>2025</v>
       </c>
       <c r="C4" t="n">
-        <v>1.465613336399713</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1.43790059505772</v>
+        <v>1.374842998568948</v>
       </c>
     </row>
     <row r="5">
@@ -508,10 +494,7 @@
         <v>2025</v>
       </c>
       <c r="C5" t="n">
-        <v>1.59693185515873</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.581449238747364</v>
+        <v>1.578298467763455</v>
       </c>
     </row>
     <row r="6">
@@ -524,10 +507,7 @@
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>1.080854416666666</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.050601549603174</v>
+        <v>1.119338896825397</v>
       </c>
     </row>
     <row r="7">
@@ -540,10 +520,7 @@
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>1.119958041666666</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.074209740079364</v>
+        <v>1.160754612012987</v>
       </c>
     </row>
     <row r="8">
@@ -556,10 +533,7 @@
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>1.088572369047619</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.057932156746031</v>
+        <v>1.128124083874459</v>
       </c>
     </row>
     <row r="9">
@@ -572,10 +546,7 @@
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>1.062724353174603</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.047267037698412</v>
+        <v>1.126009988095238</v>
       </c>
     </row>
     <row r="10">
@@ -588,10 +559,7 @@
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>1.382215025656695</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.373694588237932</v>
+        <v>1.357477024128652</v>
       </c>
     </row>
     <row r="11">
@@ -604,10 +572,7 @@
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>1.195543341089466</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.106809060425685</v>
+        <v>1.182051768205479</v>
       </c>
     </row>
     <row r="12">
@@ -620,10 +585,7 @@
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>1.571706666056166</v>
-      </c>
-      <c r="D12" t="n">
-        <v>1.56493277379565</v>
+        <v>1.511977786013383</v>
       </c>
     </row>
     <row r="13">
@@ -636,10 +598,7 @@
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>1.567724700563326</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1.548474123362748</v>
+        <v>1.532243498593447</v>
       </c>
     </row>
     <row r="14">
@@ -652,10 +611,7 @@
         <v>2025</v>
       </c>
       <c r="C14" t="n">
-        <v>1.35065815552211</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1.338858766577721</v>
+        <v>1.286310816207567</v>
       </c>
     </row>
     <row r="15">
@@ -668,10 +624,7 @@
         <v>2025</v>
       </c>
       <c r="C15" t="n">
-        <v>1.661114880615931</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1.650097965583251</v>
+        <v>1.599687076078204</v>
       </c>
     </row>
     <row r="16">
@@ -684,10 +637,7 @@
         <v>2025</v>
       </c>
       <c r="C16" t="n">
-        <v>1.517964771915585</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1.518424508928572</v>
+        <v>1.542505726460165</v>
       </c>
     </row>
     <row r="17">
@@ -700,10 +650,7 @@
         <v>2025</v>
       </c>
       <c r="C17" t="n">
-        <v>1.184007073232322</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1.100398773809524</v>
+        <v>1.22116780584693</v>
       </c>
     </row>
     <row r="18">
@@ -716,10 +663,7 @@
         <v>2025</v>
       </c>
       <c r="C18" t="n">
-        <v>1.297026954004328</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1.266523109376734</v>
+        <v>1.264910225914299</v>
       </c>
     </row>
     <row r="19">
@@ -732,10 +676,7 @@
         <v>2025</v>
       </c>
       <c r="C19" t="n">
-        <v>1.640994842352093</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1.649508123737374</v>
+        <v>1.622621357837832</v>
       </c>
     </row>
     <row r="20">
@@ -748,10 +689,7 @@
         <v>2025</v>
       </c>
       <c r="C20" t="n">
-        <v>1.290985803932179</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1.280547584054835</v>
+        <v>1.34753707240676</v>
       </c>
     </row>
     <row r="21">
@@ -764,10 +702,7 @@
         <v>2025</v>
       </c>
       <c r="C21" t="n">
-        <v>1.235658057789433</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1.23488353397991</v>
+        <v>1.198751617063492</v>
       </c>
     </row>
     <row r="22">
@@ -780,10 +715,7 @@
         <v>2025</v>
       </c>
       <c r="C22" t="n">
-        <v>1.486780000319126</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1.48614615508103</v>
+        <v>1.369754039020935</v>
       </c>
     </row>
     <row r="23">
@@ -796,10 +728,7 @@
         <v>2025</v>
       </c>
       <c r="C23" t="n">
-        <v>1.533591108111917</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1.5316777404518</v>
+        <v>1.477908774364342</v>
       </c>
     </row>
     <row r="24">
@@ -812,10 +741,7 @@
         <v>2025</v>
       </c>
       <c r="C24" t="n">
-        <v>1.519202301046177</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1.503362713883339</v>
+        <v>1.473259745066135</v>
       </c>
     </row>
     <row r="25">
@@ -828,10 +754,7 @@
         <v>2025</v>
       </c>
       <c r="C25" t="n">
-        <v>1.387749219131208</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1.376499329594302</v>
+        <v>1.392479418019133</v>
       </c>
     </row>
     <row r="26">
@@ -844,10 +767,7 @@
         <v>2025</v>
       </c>
       <c r="C26" t="n">
-        <v>1.642318459776335</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1.641735522546897</v>
+        <v>1.566771141664963</v>
       </c>
     </row>
     <row r="27">
@@ -860,10 +780,7 @@
         <v>2025</v>
       </c>
       <c r="C27" t="n">
-        <v>1.244065982572982</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1.23309786550949</v>
+        <v>1.239243227393561</v>
       </c>
     </row>
     <row r="28">
@@ -876,10 +793,7 @@
         <v>2025</v>
       </c>
       <c r="C28" t="n">
-        <v>1.040313490079365</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1.040313490079365</v>
+        <v>1.089754408369408</v>
       </c>
     </row>
     <row r="29">
@@ -892,10 +806,7 @@
         <v>2025</v>
       </c>
       <c r="C29" t="n">
-        <v>1.178556906565656</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1.096211809523809</v>
+        <v>1.174271993750401</v>
       </c>
     </row>
     <row r="30">
@@ -908,10 +819,7 @@
         <v>2025</v>
       </c>
       <c r="C30" t="n">
-        <v>1.395657796536796</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1.396004954365079</v>
+        <v>1.377656965646512</v>
       </c>
     </row>
     <row r="31">
@@ -924,10 +832,7 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>1.300498767857143</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1.282810612914864</v>
+        <v>1.304530763588263</v>
       </c>
     </row>
     <row r="32">
@@ -940,10 +845,7 @@
         <v>2025</v>
       </c>
       <c r="C32" t="n">
-        <v>1.436864606962483</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1.393641678193881</v>
+        <v>1.403568926578123</v>
       </c>
     </row>
     <row r="33">
@@ -956,10 +858,7 @@
         <v>2025</v>
       </c>
       <c r="C33" t="n">
-        <v>1.832843726190477</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1.798570781443638</v>
+        <v>1.8987477740454</v>
       </c>
     </row>
     <row r="34">
@@ -972,10 +871,7 @@
         <v>2025</v>
       </c>
       <c r="C34" t="n">
-        <v>1.267765405192031</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1.244544037948164</v>
+        <v>1.259213732002384</v>
       </c>
     </row>
     <row r="35">
@@ -988,10 +884,7 @@
         <v>2025</v>
       </c>
       <c r="C35" t="n">
-        <v>1.257693105769231</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1.236962710747586</v>
+        <v>1.261275448023596</v>
       </c>
     </row>
     <row r="36">
@@ -1004,10 +897,7 @@
         <v>2025</v>
       </c>
       <c r="C36" t="n">
-        <v>1.487244880550006</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1.485842852772228</v>
+        <v>1.463867783467783</v>
       </c>
     </row>
     <row r="37">
@@ -1020,10 +910,7 @@
         <v>2025</v>
       </c>
       <c r="C37" t="n">
-        <v>1.498106623515373</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1.482589437007437</v>
+        <v>1.445765787302533</v>
       </c>
     </row>
     <row r="38">
@@ -1036,10 +923,7 @@
         <v>2025</v>
       </c>
       <c r="C38" t="n">
-        <v>1.459610278860029</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1.438452426406926</v>
+        <v>1.42622181750462</v>
       </c>
     </row>
     <row r="39">
@@ -1052,10 +936,7 @@
         <v>2025</v>
       </c>
       <c r="C39" t="n">
-        <v>1.103337309523809</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1.064715156746031</v>
+        <v>1.130244983044733</v>
       </c>
     </row>
     <row r="40">
@@ -1068,10 +949,7 @@
         <v>2025</v>
       </c>
       <c r="C40" t="n">
-        <v>1.109357892857143</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1.070089240079364</v>
+        <v>1.146105231060606</v>
       </c>
     </row>
     <row r="41">
@@ -1084,10 +962,7 @@
         <v>2025</v>
       </c>
       <c r="C41" t="n">
-        <v>1.538278867560801</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1.53800001618995</v>
+        <v>1.473308938335631</v>
       </c>
     </row>
     <row r="42">
@@ -1100,10 +975,7 @@
         <v>2025</v>
       </c>
       <c r="C42" t="n">
-        <v>1.385726738972478</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1.378218712711185</v>
+        <v>1.390095450396952</v>
       </c>
     </row>
     <row r="43">
@@ -1116,10 +988,7 @@
         <v>2025</v>
       </c>
       <c r="C43" t="n">
-        <v>1.285000035353535</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1.261200208333334</v>
+        <v>1.270140711647636</v>
       </c>
     </row>
     <row r="44">
@@ -1132,10 +1001,7 @@
         <v>2025</v>
       </c>
       <c r="C44" t="n">
-        <v>1.294233996392495</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1.274248689213564</v>
+        <v>1.302229949304995</v>
       </c>
     </row>
     <row r="45">
@@ -1148,10 +1014,7 @@
         <v>2025</v>
       </c>
       <c r="C45" t="n">
-        <v>2.039317713092462</v>
-      </c>
-      <c r="D45" t="n">
-        <v>2.032679169441668</v>
+        <v>1.95134128154255</v>
       </c>
     </row>
     <row r="46">
@@ -1164,10 +1027,7 @@
         <v>2025</v>
       </c>
       <c r="C46" t="n">
-        <v>1.381564125595358</v>
-      </c>
-      <c r="D46" t="n">
-        <v>1.378734437278284</v>
+        <v>1.360779943136206</v>
       </c>
     </row>
     <row r="47">
@@ -1180,10 +1040,7 @@
         <v>2025</v>
       </c>
       <c r="C47" t="n">
-        <v>1.634954904761904</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1.595180633241757</v>
+        <v>1.554294892558213</v>
       </c>
     </row>
     <row r="48">
@@ -1196,10 +1053,7 @@
         <v>2025</v>
       </c>
       <c r="C48" t="n">
-        <v>1.738298739814925</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1.739575057149551</v>
+        <v>1.728799092432925</v>
       </c>
     </row>
     <row r="49">
@@ -1212,10 +1066,7 @@
         <v>2025</v>
       </c>
       <c r="C49" t="n">
-        <v>1.822261323023469</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1.82693689862915</v>
+        <v>1.834325526682367</v>
       </c>
     </row>
     <row r="50">
@@ -1228,10 +1079,7 @@
         <v>2025</v>
       </c>
       <c r="C50" t="n">
-        <v>1.400808635215623</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1.393435879106046</v>
+        <v>1.384984183881055</v>
       </c>
     </row>
     <row r="51">
@@ -1244,10 +1092,7 @@
         <v>2025</v>
       </c>
       <c r="C51" t="n">
-        <v>1.503552709810658</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1.487974471459096</v>
+        <v>1.482213815612473</v>
       </c>
     </row>
     <row r="52">
@@ -1260,10 +1105,7 @@
         <v>2025</v>
       </c>
       <c r="C52" t="n">
-        <v>1.540493440222304</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1.537683198873009</v>
+        <v>1.501495415837685</v>
       </c>
     </row>
     <row r="53">
@@ -1276,10 +1118,7 @@
         <v>2025</v>
       </c>
       <c r="C53" t="n">
-        <v>1.389495422615816</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1.37378777984238</v>
+        <v>1.352069353651571</v>
       </c>
     </row>
     <row r="54">
@@ -1292,10 +1131,7 @@
         <v>2025</v>
       </c>
       <c r="C54" t="n">
-        <v>1.379237742780069</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1.377393542665668</v>
+        <v>1.343125822353909</v>
       </c>
     </row>
     <row r="55">
@@ -1308,10 +1144,7 @@
         <v>2025</v>
       </c>
       <c r="C55" t="n">
-        <v>1.062222490079364</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1.063683490079365</v>
+        <v>1.11140801984127</v>
       </c>
     </row>
     <row r="56">
@@ -1324,10 +1157,7 @@
         <v>2025</v>
       </c>
       <c r="C56" t="n">
-        <v>1.656104008151795</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1.661976572365358</v>
+        <v>1.587269050543935</v>
       </c>
     </row>
     <row r="57">
@@ -1340,10 +1170,7 @@
         <v>2025</v>
       </c>
       <c r="C57" t="n">
-        <v>1.548067824253304</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1.540747093650572</v>
+        <v>1.512137177987285</v>
       </c>
     </row>
     <row r="58">
@@ -1356,10 +1183,7 @@
         <v>2025</v>
       </c>
       <c r="C58" t="n">
-        <v>1.407205980991923</v>
-      </c>
-      <c r="D58" t="n">
-        <v>1.382666589108179</v>
+        <v>1.373033164802629</v>
       </c>
     </row>
     <row r="59">
@@ -1372,10 +1196,7 @@
         <v>2025</v>
       </c>
       <c r="C59" t="n">
-        <v>2.459845101731603</v>
-      </c>
-      <c r="D59" t="n">
-        <v>2.406451995657122</v>
+        <v>2.344992777777777</v>
       </c>
     </row>
     <row r="60">
@@ -1388,10 +1209,7 @@
         <v>2025</v>
       </c>
       <c r="C60" t="n">
-        <v>1.533080288554526</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1.532959683395796</v>
+        <v>1.483422840522748</v>
       </c>
     </row>
     <row r="61">
@@ -1404,10 +1222,7 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>1.242127311938063</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1.240879240509491</v>
+        <v>1.278077124623183</v>
       </c>
     </row>
     <row r="62">
@@ -1420,10 +1235,7 @@
         <v>2025</v>
       </c>
       <c r="C62" t="n">
-        <v>1.068045865079365</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1.053411049603175</v>
+        <v>1.123945464285714</v>
       </c>
     </row>
     <row r="63">
@@ -1436,10 +1248,7 @@
         <v>2025</v>
       </c>
       <c r="C63" t="n">
-        <v>1.294637494047619</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1.259811067890444</v>
+        <v>1.271754861449325</v>
       </c>
     </row>
     <row r="64">
@@ -1452,10 +1261,7 @@
         <v>2025</v>
       </c>
       <c r="C64" t="n">
-        <v>1.060571811507936</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1.046873371031745</v>
+        <v>1.131032784632035</v>
       </c>
     </row>
     <row r="65">
@@ -1468,10 +1274,7 @@
         <v>2025</v>
       </c>
       <c r="C65" t="n">
-        <v>1.729289370345157</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1.709842263268389</v>
+        <v>1.69147378749845</v>
       </c>
     </row>
     <row r="66">
@@ -1484,10 +1287,7 @@
         <v>2025</v>
       </c>
       <c r="C66" t="n">
-        <v>1.546887673400674</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1.541293064273689</v>
+        <v>1.488300456346083</v>
       </c>
     </row>
     <row r="67">
@@ -1500,10 +1300,7 @@
         <v>2025</v>
       </c>
       <c r="C67" t="n">
-        <v>1.052479799603174</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1.052479799603174</v>
+        <v>1.132552700396825</v>
       </c>
     </row>
     <row r="68">
@@ -1516,10 +1313,7 @@
         <v>2025</v>
       </c>
       <c r="C68" t="n">
-        <v>1.264224548049174</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1.243175339535465</v>
+        <v>1.298320051135566</v>
       </c>
     </row>
     <row r="69">
@@ -1532,10 +1326,7 @@
         <v>2025</v>
       </c>
       <c r="C69" t="n">
-        <v>1.184434231962481</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1.105948892857143</v>
+        <v>1.148547613636363</v>
       </c>
     </row>
     <row r="70">
@@ -1548,10 +1339,7 @@
         <v>2025</v>
       </c>
       <c r="C70" t="n">
-        <v>1.252879704795205</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1.231263014138639</v>
+        <v>1.232587168054022</v>
       </c>
     </row>
     <row r="71">
@@ -1564,10 +1352,7 @@
         <v>2025</v>
       </c>
       <c r="C71" t="n">
-        <v>1.17998718037518</v>
-      </c>
-      <c r="D71" t="n">
-        <v>1.100575345238095</v>
+        <v>1.203765327380952</v>
       </c>
     </row>
     <row r="72">
@@ -1580,10 +1365,7 @@
         <v>2025</v>
       </c>
       <c r="C72" t="n">
-        <v>1.087110261904762</v>
-      </c>
-      <c r="D72" t="n">
-        <v>1.055320740079365</v>
+        <v>1.127351059523809</v>
       </c>
     </row>
     <row r="73">
@@ -1596,10 +1378,7 @@
         <v>2025</v>
       </c>
       <c r="C73" t="n">
-        <v>1.707719704365359</v>
-      </c>
-      <c r="D73" t="n">
-        <v>1.702872508487407</v>
+        <v>1.688287679137903</v>
       </c>
     </row>
     <row r="74">
@@ -1612,10 +1391,7 @@
         <v>2025</v>
       </c>
       <c r="C74" t="n">
-        <v>1.385649023327154</v>
-      </c>
-      <c r="D74" t="n">
-        <v>1.379101932880862</v>
+        <v>1.365438053216675</v>
       </c>
     </row>
     <row r="75">
@@ -1628,10 +1404,7 @@
         <v>2025</v>
       </c>
       <c r="C75" t="n">
-        <v>1.296922121031745</v>
-      </c>
-      <c r="D75" t="n">
-        <v>1.265085903388278</v>
+        <v>1.266988098029756</v>
       </c>
     </row>
     <row r="76">
@@ -1644,26 +1417,20 @@
         <v>2025</v>
       </c>
       <c r="C76" t="n">
-        <v>1.472994753066379</v>
-      </c>
-      <c r="D76" t="n">
-        <v>1.466224592352092</v>
+        <v>1.390130587904572</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ханты-Мансийский автономный округ - Югра</t>
+          <t>Ханты-Мансийский авт.округ-Югра</t>
         </is>
       </c>
       <c r="B77" t="n">
         <v>2025</v>
       </c>
       <c r="C77" t="n">
-        <v>1.652842965583252</v>
-      </c>
-      <c r="D77" t="n">
-        <v>1.655110860424521</v>
+        <v>1.602482819272921</v>
       </c>
     </row>
     <row r="78">
@@ -1676,10 +1443,7 @@
         <v>2025</v>
       </c>
       <c r="C78" t="n">
-        <v>1.441832563492064</v>
-      </c>
-      <c r="D78" t="n">
-        <v>1.404039217939917</v>
+        <v>1.392770165546245</v>
       </c>
     </row>
     <row r="79">
@@ -1692,10 +1456,7 @@
         <v>2025</v>
       </c>
       <c r="C79" t="n">
-        <v>2.649130948232323</v>
-      </c>
-      <c r="D79" t="n">
-        <v>2.634626664502165</v>
+        <v>2.41113508531746</v>
       </c>
     </row>
     <row r="80">
@@ -1708,10 +1469,7 @@
         <v>2025</v>
       </c>
       <c r="C80" t="n">
-        <v>1.384772848571354</v>
-      </c>
-      <c r="D80" t="n">
-        <v>1.381773772638327</v>
+        <v>1.357537632147026</v>
       </c>
     </row>
     <row r="81">
@@ -1724,10 +1482,7 @@
         <v>2025</v>
       </c>
       <c r="C81" t="n">
-        <v>1.651541644154681</v>
-      </c>
-      <c r="D81" t="n">
-        <v>1.662197906059443</v>
+        <v>1.642367243119162</v>
       </c>
     </row>
     <row r="82">
@@ -1740,10 +1495,7 @@
         <v>2025</v>
       </c>
       <c r="C82" t="n">
-        <v>1.909437232683983</v>
-      </c>
-      <c r="D82" t="n">
-        <v>1.906482240079365</v>
+        <v>1.882006791128725</v>
       </c>
     </row>
     <row r="83">
@@ -1756,10 +1508,7 @@
         <v>2025</v>
       </c>
       <c r="C83" t="n">
-        <v>1.280010443070819</v>
-      </c>
-      <c r="D83" t="n">
-        <v>1.246007565906316</v>
+        <v>1.256497183262227</v>
       </c>
     </row>
     <row r="84">
@@ -1772,10 +1521,7 @@
         <v>2025</v>
       </c>
       <c r="C84" t="n">
-        <v>1.401762851406135</v>
-      </c>
-      <c r="D84" t="n">
-        <v>1.39945557785942</v>
+        <v>1.380726119763467</v>
       </c>
     </row>
     <row r="85">
@@ -1788,10 +1534,7 @@
         <v>2025</v>
       </c>
       <c r="C85" t="n">
-        <v>1.248971165112666</v>
-      </c>
-      <c r="D85" t="n">
-        <v>1.245389347652349</v>
+        <v>1.291422424316546</v>
       </c>
     </row>
     <row r="86">
@@ -1804,10 +1547,7 @@
         <v>2025</v>
       </c>
       <c r="C86" t="n">
-        <v>1.061944382936507</v>
-      </c>
-      <c r="D86" t="n">
-        <v>1.063405382936508</v>
+        <v>1.113201918290044</v>
       </c>
     </row>
   </sheetData>

--- a/notebooks/Random Forest/predictions_afr_2025.xlsx
+++ b/notebooks/Random Forest/predictions_afr_2025.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>СКР_прогноз</t>
+          <t>predictions</t>
         </is>
       </c>
     </row>
@@ -455,7 +455,7 @@
         <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>1.271219715578256</v>
+        <v>1.271219715578257</v>
       </c>
     </row>
     <row r="3">
@@ -585,7 +585,7 @@
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>1.511977786013383</v>
+        <v>1.511977786013382</v>
       </c>
     </row>
     <row r="13">
@@ -598,7 +598,7 @@
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>1.532243498593447</v>
+        <v>1.532243498593446</v>
       </c>
     </row>
     <row r="14">
@@ -624,7 +624,7 @@
         <v>2025</v>
       </c>
       <c r="C15" t="n">
-        <v>1.599687076078204</v>
+        <v>1.599687076078203</v>
       </c>
     </row>
     <row r="16">
@@ -637,7 +637,7 @@
         <v>2025</v>
       </c>
       <c r="C16" t="n">
-        <v>1.542505726460165</v>
+        <v>1.542505726460164</v>
       </c>
     </row>
     <row r="17">
@@ -650,7 +650,7 @@
         <v>2025</v>
       </c>
       <c r="C17" t="n">
-        <v>1.22116780584693</v>
+        <v>1.221167805846931</v>
       </c>
     </row>
     <row r="18">
@@ -741,7 +741,7 @@
         <v>2025</v>
       </c>
       <c r="C24" t="n">
-        <v>1.473259745066135</v>
+        <v>1.473259745066134</v>
       </c>
     </row>
     <row r="25">
@@ -754,7 +754,7 @@
         <v>2025</v>
       </c>
       <c r="C25" t="n">
-        <v>1.392479418019133</v>
+        <v>1.392479418019134</v>
       </c>
     </row>
     <row r="26">
@@ -767,7 +767,7 @@
         <v>2025</v>
       </c>
       <c r="C26" t="n">
-        <v>1.566771141664963</v>
+        <v>1.566771141664962</v>
       </c>
     </row>
     <row r="27">
@@ -793,7 +793,7 @@
         <v>2025</v>
       </c>
       <c r="C28" t="n">
-        <v>1.089754408369408</v>
+        <v>1.089754408369409</v>
       </c>
     </row>
     <row r="29">
@@ -858,7 +858,7 @@
         <v>2025</v>
       </c>
       <c r="C33" t="n">
-        <v>1.8987477740454</v>
+        <v>1.898747774045401</v>
       </c>
     </row>
     <row r="34">
@@ -884,7 +884,7 @@
         <v>2025</v>
       </c>
       <c r="C35" t="n">
-        <v>1.261275448023596</v>
+        <v>1.261275448023597</v>
       </c>
     </row>
     <row r="36">
@@ -1014,7 +1014,7 @@
         <v>2025</v>
       </c>
       <c r="C45" t="n">
-        <v>1.95134128154255</v>
+        <v>1.951341281542551</v>
       </c>
     </row>
     <row r="46">
@@ -1053,7 +1053,7 @@
         <v>2025</v>
       </c>
       <c r="C48" t="n">
-        <v>1.728799092432925</v>
+        <v>1.728799092432924</v>
       </c>
     </row>
     <row r="49">
@@ -1131,7 +1131,7 @@
         <v>2025</v>
       </c>
       <c r="C54" t="n">
-        <v>1.343125822353909</v>
+        <v>1.34312582235391</v>
       </c>
     </row>
     <row r="55">
@@ -1170,7 +1170,7 @@
         <v>2025</v>
       </c>
       <c r="C57" t="n">
-        <v>1.512137177987285</v>
+        <v>1.512137177987284</v>
       </c>
     </row>
     <row r="58">
@@ -1183,7 +1183,7 @@
         <v>2025</v>
       </c>
       <c r="C58" t="n">
-        <v>1.373033164802629</v>
+        <v>1.37303316480263</v>
       </c>
     </row>
     <row r="59">
@@ -1222,7 +1222,7 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>1.278077124623183</v>
+        <v>1.278077124623184</v>
       </c>
     </row>
     <row r="62">
@@ -1274,7 +1274,7 @@
         <v>2025</v>
       </c>
       <c r="C65" t="n">
-        <v>1.69147378749845</v>
+        <v>1.691473787498449</v>
       </c>
     </row>
     <row r="66">
@@ -1313,7 +1313,7 @@
         <v>2025</v>
       </c>
       <c r="C68" t="n">
-        <v>1.298320051135566</v>
+        <v>1.298320051135565</v>
       </c>
     </row>
     <row r="69">
@@ -1326,7 +1326,7 @@
         <v>2025</v>
       </c>
       <c r="C69" t="n">
-        <v>1.148547613636363</v>
+        <v>1.148547613636364</v>
       </c>
     </row>
     <row r="70">
@@ -1365,7 +1365,7 @@
         <v>2025</v>
       </c>
       <c r="C72" t="n">
-        <v>1.127351059523809</v>
+        <v>1.12735105952381</v>
       </c>
     </row>
     <row r="73">
@@ -1404,7 +1404,7 @@
         <v>2025</v>
       </c>
       <c r="C75" t="n">
-        <v>1.266988098029756</v>
+        <v>1.266988098029757</v>
       </c>
     </row>
     <row r="76">
@@ -1430,7 +1430,7 @@
         <v>2025</v>
       </c>
       <c r="C77" t="n">
-        <v>1.602482819272921</v>
+        <v>1.60248281927292</v>
       </c>
     </row>
     <row r="78">
@@ -1482,7 +1482,7 @@
         <v>2025</v>
       </c>
       <c r="C81" t="n">
-        <v>1.642367243119162</v>
+        <v>1.642367243119161</v>
       </c>
     </row>
     <row r="82">
@@ -1495,7 +1495,7 @@
         <v>2025</v>
       </c>
       <c r="C82" t="n">
-        <v>1.882006791128725</v>
+        <v>1.882006791128724</v>
       </c>
     </row>
     <row r="83">
@@ -1521,7 +1521,7 @@
         <v>2025</v>
       </c>
       <c r="C84" t="n">
-        <v>1.380726119763467</v>
+        <v>1.380726119763469</v>
       </c>
     </row>
     <row r="85">
